--- a/CodeSystem-sf-BetNutChewBeh-codesystem.xlsx
+++ b/CodeSystem-sf-BetNutChewBeh-codesystem.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T21:42:02+08:00</t>
+    <t>2026-07-10T19:56:53+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-sf-BetNutChewBeh-codesystem.xlsx
+++ b/CodeSystem-sf-BetNutChewBeh-codesystem.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T19:56:53+08:00</t>
+    <t>2026-07-10T21:30:50+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-sf-BetNutChewBeh-codesystem.xlsx
+++ b/CodeSystem-sf-BetNutChewBeh-codesystem.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T21:30:50+08:00</t>
+    <t>2026-07-23T22:22:27+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-sf-BetNutChewBeh-codesystem.xlsx
+++ b/CodeSystem-sf-BetNutChewBeh-codesystem.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T22:22:27+08:00</t>
+    <t>2026-07-24T13:54:16+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-sf-BetNutChewBeh-codesystem.xlsx
+++ b/CodeSystem-sf-BetNutChewBeh-codesystem.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-24T13:54:16+08:00</t>
+    <t>2026-07-25T16:18:15+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-sf-BetNutChewBeh-codesystem.xlsx
+++ b/CodeSystem-sf-BetNutChewBeh-codesystem.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-25T16:18:15+08:00</t>
+    <t>2026-07-26T10:07:44+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-sf-BetNutChewBeh-codesystem.xlsx
+++ b/CodeSystem-sf-BetNutChewBeh-codesystem.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T10:07:44+08:00</t>
+    <t>2026-07-26T12:18:37+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-sf-BetNutChewBeh-codesystem.xlsx
+++ b/CodeSystem-sf-BetNutChewBeh-codesystem.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T12:18:37+08:00</t>
+    <t>2026-07-26T14:28:30+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-sf-BetNutChewBeh-codesystem.xlsx
+++ b/CodeSystem-sf-BetNutChewBeh-codesystem.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T14:28:30+08:00</t>
+    <t>2026-07-26T15:21:49+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-sf-BetNutChewBeh-codesystem.xlsx
+++ b/CodeSystem-sf-BetNutChewBeh-codesystem.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T15:21:49+08:00</t>
+    <t>2026-07-26T16:11:18+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-sf-BetNutChewBeh-codesystem.xlsx
+++ b/CodeSystem-sf-BetNutChewBeh-codesystem.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T16:11:18+08:00</t>
+    <t>2026-07-26T18:45:10+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-sf-BetNutChewBeh-codesystem.xlsx
+++ b/CodeSystem-sf-BetNutChewBeh-codesystem.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="48">
   <si>
     <t>Property</t>
   </si>
@@ -42,54 +42,63 @@
     <t>Title</t>
   </si>
   <si>
+    <t>【本地 stub】Betel Nut Chewing Behavior Code System（非權威定義）</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>draft</t>
+  </si>
+  <si>
+    <t>Experimental</t>
+  </si>
+  <si>
+    <t>true</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>2026-07-29T09:46:30+00:00</t>
+  </si>
+  <si>
+    <t>Publisher</t>
+  </si>
+  <si>
+    <t>衛生福利部次世代數位醫療平臺專案辦公室 &amp; 長庚醫療財團法人長庚紀念醫院</t>
+  </si>
+  <si>
+    <t>Contact</t>
+  </si>
+  <si>
+    <t>衛生福利部次世代數位醫療平臺專案辦公室 &amp; 長庚醫療財團法人長庚紀念醫院 (https://twcore.mohw.gov.tw/twregistry/)</t>
+  </si>
+  <si>
+    <t>衛生福利部次世代數位醫療平臺專案辦公室 (https://twcore.mohw.gov.tw/twregistry/)</t>
+  </si>
+  <si>
+    <t>Jurisdiction</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
     <t>Betel Nut Chewing Behavior Code System</t>
   </si>
   <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>active</t>
-  </si>
-  <si>
-    <t>Experimental</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>2026-07-26T18:45:10+08:00</t>
-  </si>
-  <si>
-    <t>Publisher</t>
-  </si>
-  <si>
-    <t>衛生福利部次世代數位醫療平臺專案辦公室 &amp; 長庚醫療財團法人長庚紀念醫院</t>
-  </si>
-  <si>
-    <t>Contact</t>
-  </si>
-  <si>
-    <t>衛生福利部次世代數位醫療平臺專案辦公室 &amp; 長庚醫療財團法人長庚紀念醫院 (https://twcore.mohw.gov.tw/twregistry/)</t>
-  </si>
-  <si>
-    <t>衛生福利部次世代數位醫療平臺專案辦公室 (https://twcore.mohw.gov.tw/twregistry/)</t>
-  </si>
-  <si>
-    <t>Jurisdiction</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
     <t>Purpose</t>
   </si>
   <si>
     <t>Copyright</t>
   </si>
   <si>
+    <t>權威定義來源為臺灣癌症登記短表 IG（TWCR_SF）。本 IG 僅為建置與驗證所需之局部複本（content = fragment），非權威定義；實作端應以 TWCR_SF 官方定義為準。</t>
+  </si>
+  <si>
     <t>Case Sensitive</t>
   </si>
   <si>
@@ -108,16 +117,13 @@
     <t>Content</t>
   </si>
   <si>
-    <t>complete</t>
+    <t>fragment</t>
   </si>
   <si>
     <t>Supplements</t>
   </si>
   <si>
     <t>Count</t>
-  </si>
-  <si>
-    <t>3</t>
   </si>
   <si>
     <t>Level</t>
@@ -343,119 +349,121 @@
       <c r="A7" t="s" s="2">
         <v>12</v>
       </c>
-      <c r="B7" s="2"/>
+      <c r="B7" t="s" s="2">
+        <v>13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>9</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>24</v>
-      </c>
-      <c r="B15" s="2"/>
+        <v>26</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>27</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B22" s="2"/>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="B23" t="s" s="2">
-        <v>34</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="B23" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -469,51 +477,51 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D4" s="2"/>
     </row>

--- a/CodeSystem-sf-BetNutChewBeh-codesystem.xlsx
+++ b/CodeSystem-sf-BetNutChewBeh-codesystem.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T09:46:30+00:00</t>
+    <t>2026-07-29T14:03:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-sf-BetNutChewBeh-codesystem.xlsx
+++ b/CodeSystem-sf-BetNutChewBeh-codesystem.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T14:03:51+00:00</t>
+    <t>2026-07-29T16:26:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-sf-BetNutChewBeh-codesystem.xlsx
+++ b/CodeSystem-sf-BetNutChewBeh-codesystem.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T16:26:07+00:00</t>
+    <t>2026-07-29T16:54:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-sf-BetNutChewBeh-codesystem.xlsx
+++ b/CodeSystem-sf-BetNutChewBeh-codesystem.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T16:54:28+00:00</t>
+    <t>2026-07-30T07:25:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-sf-BetNutChewBeh-codesystem.xlsx
+++ b/CodeSystem-sf-BetNutChewBeh-codesystem.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T07:25:13+00:00</t>
+    <t>2026-07-30T09:28:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-sf-BetNutChewBeh-codesystem.xlsx
+++ b/CodeSystem-sf-BetNutChewBeh-codesystem.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T09:28:37+00:00</t>
+    <t>2026-07-30T10:44:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-sf-BetNutChewBeh-codesystem.xlsx
+++ b/CodeSystem-sf-BetNutChewBeh-codesystem.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T10:44:37+00:00</t>
+    <t>2026-07-30T12:17:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-sf-BetNutChewBeh-codesystem.xlsx
+++ b/CodeSystem-sf-BetNutChewBeh-codesystem.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T12:17:12+00:00</t>
+    <t>2026-07-30T14:17:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-sf-BetNutChewBeh-codesystem.xlsx
+++ b/CodeSystem-sf-BetNutChewBeh-codesystem.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T14:17:56+00:00</t>
+    <t>2026-07-30T14:46:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-sf-BetNutChewBeh-codesystem.xlsx
+++ b/CodeSystem-sf-BetNutChewBeh-codesystem.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T14:46:31+00:00</t>
+    <t>2026-08-05T16:28:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-sf-BetNutChewBeh-codesystem.xlsx
+++ b/CodeSystem-sf-BetNutChewBeh-codesystem.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>0.2.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T16:28:11+00:00</t>
+    <t>2026-08-05T16:48:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-sf-BetNutChewBeh-codesystem.xlsx
+++ b/CodeSystem-sf-BetNutChewBeh-codesystem.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.1</t>
+    <t>0.2.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T16:48:01+00:00</t>
+    <t>2026-08-17T03:02:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-sf-BetNutChewBeh-codesystem.xlsx
+++ b/CodeSystem-sf-BetNutChewBeh-codesystem.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.3</t>
+    <t>0.2.4</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-17T03:02:16+00:00</t>
+    <t>2026-08-17T05:27:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-sf-BetNutChewBeh-codesystem.xlsx
+++ b/CodeSystem-sf-BetNutChewBeh-codesystem.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.4</t>
+    <t>0.2.5</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-17T05:27:05+00:00</t>
+    <t>2026-08-17T06:57:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
